--- a/prototypes/results/2026-09-19_shag4_partiya3_slabye.xlsx
+++ b/prototypes/results/2026-09-19_shag4_partiya3_slabye.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Партия 3 - слабые" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как заполнить" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Партия 3 - слабые" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Как заполнить" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,7 +606,6 @@
         <v>0.497</v>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -674,7 +673,11 @@
         <v>0.496</v>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Полный поиск по ФРСН: точной нормы "устройство бетонной подготовки" нет. Ближайший аналог -- Н-07-02-035-03-01 "Укладка бетонной смеси в массивы и отдельные фундаменты, подача краном в бадьях/бетононасосом, объём конструкции до 10 м3", чел-ч 0,33, звено Бетонщик 2/4 разр. Профессия совпадает с вашей пометкой. Приблизительно -- способ подачи бетона не уточнён.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -742,7 +745,6 @@
         <v>0.49</v>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -810,7 +812,6 @@
         <v>0.491</v>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -878,7 +879,11 @@
         <v>0.471</v>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Профессия электромонтажник в ФРСН нашлась только у Н-55-05-014-05-01 "Подготовка к включению: предохранителей", чел-ч 0,06, Электромонтажник по вторичным цепям 4 разр. ВНИМАНИЕ: это про электрические предохранители (плавкие вставки), а не про огневой предохранитель ПО-50/ОП-ААН (это устройство защиты от распространения пламени на трубопроводах -- механическое/арматурное изделие). Похоже на словарную ловушку по омониму "предохранитель". Нужна ваша проверка -- уверенности нет.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -946,7 +951,11 @@
         <v>0.456</v>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Отдельной нормы на промышленную окраску металла эмалью ПФ-115 с антикоррозионной огрунтовкой в ФРСН нет. Ближайший аналог -- сборник 30 (ремонт зданий), серия Н-30-10-013 "Окрашивание металлических поверхностей масляными составами" (расчистка -&gt; первое окрашивание -&gt; второе окрашивание), звено Маляр. Предлагаю Н-30-10-013-43-01 "второе окрашивание кистью", чел-ч 2,4. Приблизительно -- контекст сборника про кровельный ремонт, не про металлоконструкции в целом.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1014,7 +1023,11 @@
         <v>0.429</v>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>УЖЕ ВЕРНО: кандидат #1 (Н-07-01-027-01-01, Гидроизоляция швов бутил-каучуковой лентой) уже имеет звено Монтажник конструкций -- ровно то, что запрошено. Возможно, при пометке 'нет' сравнивался кандидат #2. Предлагаю оставить кандидата #1 как есть.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1082,7 +1095,11 @@
         <v>0.478</v>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>После полного поиска (профессия не задавалась -- ваша пометка "монтажник МК" не нашла прямого совпадения) хорошего аналога на покрытие кабеля сигнальной лентой в траншее не нашлось -- лучшие кандидаты (прокладка сигнального троса, окрашивание кабелей) не по теме именно защитной ленты.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1150,7 +1167,11 @@
         <v>0.443</v>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>УЖЕ ВЕРНО: кандидат #1 (Н-38-01-016-58-01, Герметизация проходов при прокладке кабеля во взрывоопасных помещениях в трубе) уже имеет звено Электромонтажник по кабельным сетям, тема точная (скор 0.644, лучший во всей партии). Предлагаю оставить кандидата #1 как есть.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1218,7 +1239,11 @@
         <v>0.48</v>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Точной нормы на "монтаж опорных конструкций для крепления трубопроводов" не нашлось. Ближайший по теме и профессии -- Н-47-01-003-01-01 "Монтаж трубопроводов и П-образных компенсаторов на подвесках внутри зданий, диаметр до 50мм", чел-ч 0,13, звено Монтажник технологических трубопроводов. Тема близкая (крепление труб), но это монтаж самой трубы на подвеске, не отдельно опорной конструкции.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1286,7 +1311,6 @@
         <v>0.482</v>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1354,7 +1378,6 @@
         <v>0.462</v>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1422,7 +1445,11 @@
         <v>0.398</v>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Н-31-07-002-02-01 "Окраска чугунных перил: огрунтовка перил масляной краской", чел-ч 2, звено Маляр 3 разр. Профессия и операция (огрунтовка) совпадают, элемент другой (перила, не общие металлоконструкции) -- чел-ч приблизительны.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1490,7 +1517,6 @@
         <v>0.473</v>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1558,7 +1584,6 @@
         <v>0.473</v>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1626,7 +1651,11 @@
         <v>0.404</v>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Отдельной нормы на огрунтовку эпоксидной грунтовкой не нашлось вообще -- эпоксидные грунтовки в ФРСН не описаны. Тот же аналог, что и для №13 (Н-31-07-002-02-01, Маляр), состав звена верен, чел-ч не соответствуют эпоксидному составу.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1694,7 +1723,6 @@
         <v>0.414</v>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1762,7 +1790,11 @@
         <v>0.445</v>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Н-53-06-005-03-01 "Установка щитка под установку инфракрасного обогрева и ультрафиолетового облучения", чел-ч 0,3, звено Монтажник 2/4 разр. Профессия монтажник совпадает с вашей пометкой, тема близкая (установка под ИК-обогрев), не точная (сам обогреватель, не щиток).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1830,7 +1862,11 @@
         <v>0.452</v>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>НАШЁЛСЯ ТОЧНЫЙ АНАЛОГ ПО ТЕМЕ: Н-07-02-040-04-01 "Установка анкерных болтов диаметром до 50мм на эпоксидном клее с его приготовлением", чел-ч 0,09 -- это и есть химический (эпоксидный) анкер. НО звено там Бетонщик, не монтажник, как вы указали. Расхождение с вашей пометкой -- какая профессия верна на практике?</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1898,7 +1934,6 @@
         <v>0.462</v>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1966,7 +2001,6 @@
         <v>0.446</v>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2034,7 +2068,11 @@
         <v>0.352</v>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>После полного поиска по корпусу (лемматизация+TF-IDF, профессия монтажник) хорошего аналога на деформационные швы в ёмкостных сооружениях с резиновыми прокладками не нашлось вообще -- лучшие кандидаты (водонагреватели, резиновые шланги в электрике) не по теме. Похоже, в ФРСН это не описано.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2102,7 +2140,6 @@
         <v>0.453</v>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2170,7 +2207,6 @@
         <v>0.44</v>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2238,7 +2274,11 @@
         <v>0.366</v>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ПРОВЕРЕНО ПО ВСЕМУ КОРПУСУ: профессии "дефектоскопист" в ФРСН нет вообще, слова "рентген", "радиограф", "гаммаграф" не встречаются ни разу ни в одном из 71 сборника. Рентген-контроль сварных швов в ФРСН просто не описан -- не ошибка поиска, факт по корпусу. Тот же класс проблемы, что и шпонка ГЭСН08-01-008-05 -- нужен отдельный источник, не ФРСН.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2306,7 +2346,6 @@
         <v>0.433</v>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2374,7 +2413,6 @@
         <v>0.352</v>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2442,7 +2480,11 @@
         <v>0.307</v>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>НАШЁЛСЯ ТОЧНЫЙ АНАЛОГ ПО ТЕМЕ: Н-07-02-010-01-01 "Установка стальных закладных деталей в опалубку, масса до 4 кг" (и далее по весу до 100 кг), чел-ч 0,29-1,4 -- это именно установка стальных элементов, остающихся в теле бетона. НО звено там Арматурщик+Плотник, не Бетонщик, как вы указали. Расхождение с вашей пометкой -- какая профессия верна на практике?</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2510,7 +2552,11 @@
         <v>0.417</v>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Н-19-04-001-02-01 "Устройство сборных железобетонных и бетонных типовых колодцев диаметром 1000мм, из отдельных колец", чел-ч 7,6, звено Монтажник наружных трубопроводов (скор 0.508, лучший среди альтернатив). ВНИМАНИЕ: профессия в ФРСН для колодцев -- именно эта специальность, не "монтажник сборных жб конструкций", как вы указали. В ФРСН колодцы идут по разделу наружных трубопроводов (сборник 19), не по жб-монтажу.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2578,7 +2624,6 @@
         <v>0.416</v>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2646,7 +2691,11 @@
         <v>0.412</v>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Отдельной нормы на антикоррозионную защиту полиуретановыми составами на высоте с перестановкой подмостей в ФРСН нет. Условный аналог -- тот же Н-30-10-013 (окраска металла маслом, сборник 30), но это не отражает ни состав (полиуретан), ни условия (высота, подмости). Похоже на нерешаемый случай без отдельного источника.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2714,7 +2763,11 @@
         <v>0.398</v>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>После полного поиска хорошего аналога на съёмные/выдвижные электронные блоки (модули, ячейки, ТЭЗ) не нашлось -- лучшие кандидаты (выдвижные ящики-мебель, ревизия трансформаторов) не по теме. Уточните, пожалуйста, к какому оборудованию относится эта позиция по факту -- легче искать по названию прибора, чем по общей формулировке.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2782,7 +2835,11 @@
         <v>0.402</v>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Тот же случай, что и №31 -- антикоррозионная защита эпоксидными составами на высоте, хорошего аналога в ФРСН нет.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2850,7 +2907,11 @@
         <v>0.318</v>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Н-09-05-006-09-01 "Отделка бетонной поверхности", чел-ч 0,47, звено Штукатур 3 разр. -- профессия штукатур подтверждена, как вы и написали. Операция приблизительная (общая отделка бетона, не конкретно набивка фриза по трафарету маслом).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2918,7 +2979,11 @@
         <v>0.38</v>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>После полного поиска хорошего аналога на комплекс измерений постоянным током парных кабелей не нашлось -- лучшие кандидаты (подключение реостата, тормозные электромагниты) не по теме.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2986,7 +3051,11 @@
         <v>0.396</v>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>После полного поиска хорошего аналога на пункт переговорной парковой связи не нашлось -- лучшие кандидаты (крепления башенного крана, установка связей металлоконструкций) не по теме.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3054,7 +3123,11 @@
         <v>0.387</v>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Прямого аналога на оклейку фотообоями в ФРСН нет (обойные работы описаны иначе). Условный аналог по профессии -- сборник 30, серия Н-30-10-012 "Окрашивание масляными составами подготовленных поверхностей", звено Маляр, но по операции это НЕ оклейка обоев, а окраска. Профессия маляр подтверждена (совпадает с решением по похожему коду ГЭСНм39-01-001-19 в партии 1, там тоже маляр), сама норма -- не подходит, нужен другой источник.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3122,7 +3195,6 @@
         <v>0.389</v>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3190,7 +3262,6 @@
         <v>0.371</v>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3258,7 +3329,6 @@
         <v>0.369</v>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3326,7 +3396,6 @@
         <v>0.367</v>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3394,7 +3463,11 @@
         <v>0.348</v>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Тот же случай, что и №31/33 -- антикоррозионное покрытие резервуара, хорошего аналога в ФРСН для промышленной антикоррозийки не нашлось.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3462,7 +3535,11 @@
         <v>0.348</v>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Н-09-06-008-01-01 "Установка металлических перил", чел-ч 0,49, звено Монтажник конструкций 3/4 разр. Профессия монтажник совпадает с вашей пометкой, тема близкая (металлическая ограждающая конструкция), не точная (перила, не решётка приямка).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3530,7 +3607,11 @@
         <v>0.339</v>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Н-27-02-002-06-01 "Поливка водой из шланга щебня и гравия перед укаткой при устройстве гравийных оснований", чел-ч 0,21, звено Дорожный рабочий 1 разр. Профессия подтверждена, тема близкая (полив материала дорожных работ), не точная (щебень/гравий, а не грунт насыпи).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3598,7 +3679,11 @@
         <v>0.343</v>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>После полного поиска хорошего аналога на монтаж унифицированных эстакад пролётом до 18м не нашлось -- лучшие кандидаты (пристрелка стативов, монтаж патрубков на эстакаде) не по теме самой эстакады.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
